--- a/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:53:12+00:00</t>
+    <t>2026-08-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:08:45+00:00</t>
+    <t>2026-08-20T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:24:46+00:00</t>
+    <t>2026-08-21T08:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T08:13:05+00:00</t>
+    <t>2026-08-23T21:45:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-23T21:45:18+00:00</t>
+    <t>2026-08-24T13:13:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:13:01+00:00</t>
+    <t>2026-08-25T11:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:34:21+00:00</t>
+    <t>2026-08-25T11:56:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:56:50+00:00</t>
+    <t>2026-08-25T20:08:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRSectionLaboratoryChapterLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T20:08:46+00:00</t>
+    <t>2026-08-31T08:09:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
